--- a/stories/arbres/TREE-SOC-009.xlsx
+++ b/stories/arbres/TREE-SOC-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara est dans la petite cuisine de l'école. Maman aide aujourd'hui. Maman dit : tu peux aider. Une tâche sûre. Laver une tomate. Poser une cuillère. Apporter le pain. Avec un adulte.</t>
+          <t>Sara est dans la petite cuisine de l'école. Maman aide aujourd'hui. Tu peux aider. Une tâche sûre. Laver une tomate. Poser une cuillère. Apporter le pain. Avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara est dans la petite cuisine de l'école. Maman aide aujourd'hui.
+maman|Tu peux aider.
+narrateur|Une tâche sûre. Laver une tomate. Poser une cuillère. Apporter le pain. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'évier, la table, ou le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers l'évier. L'eau est froide. maman est tout près. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sara aide en cuisine. Comment ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sara a retenu. Sara fait une tâche sûre. Avec un adulte. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la tomate, la cuillère, ou le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la tomate. La cuillère tinte. maman montre lentement. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint laver. Maman est près. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la tomate.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint poser. Ça sent le basilic. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la tomate.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint apporter. Les mains sont mouillées. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la tomate.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3754,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la cuillère. La table est lisse. maman montre lentement. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3949,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4116,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint laver. Ça sent le basilic. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4283,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4450,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint poser. Les mains sont mouillées. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4617,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4784,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint apporter. Un camarade attend. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4951,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5118,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le pain. Le panier est osier. maman montre lentement. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5179,6 +5313,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5341,6 +5480,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint laver. Les mains sont mouillées. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5647,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5814,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint poser. Un camarade attend. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5981,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6148,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint apporter. La lumière est claire. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6315,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6482,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers la table. La tomate est lisse. maman est tout près. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6491,6 +6665,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Sara aide en cuisine. Comment ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6515,7 +6694,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Sara respire. Sara fait une tâche sûre. Avec un adulte. maman dit : je suis là.</t>
+          <t>Sara respire. Sara fait une tâche sûre. Avec un adulte. Je suis là.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6657,6 +6836,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Sara respire. Sara fait une tâche sûre. Avec un adulte.
+maman|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7028,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la tomate, la cuillère, ou le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7195,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la tomate. Maman est près. maman montre lentement. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7390,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7357,6 +7557,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint laver. Ça sent le basilic. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la tomate.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7724,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7891,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint poser. Les mains sont mouillées. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la tomate.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8058,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8225,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint apporter. Un camarade attend. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la tomate.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8392,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8559,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la cuillère. Ça sent le basilic. maman montre lentement. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8519,6 +8754,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8681,6 +8921,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint laver. Les mains sont mouillées. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9088,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9255,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint poser. Un camarade attend. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9422,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9589,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint apporter. La lumière est claire. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9756,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9923,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le pain. Les mains sont mouillées. maman montre lentement. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9843,6 +10118,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10005,6 +10285,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint laver. Un camarade attend. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10452,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10619,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint poser. La lumière est claire. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10786,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10953,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint apporter. Un oiseau chante. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11120,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10977,6 +11287,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le panier. Le pain sent bon. maman est tout près. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Sara aide en cuisine. Comment ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|C'est juste. Sara fait une tâche sûre. Avec un adulte. Sara donne la main à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la tomate, la cuillère, ou le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la tomate. Un camarade attend. maman montre lentement. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11859,6 +12194,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint laver. Les mains sont mouillées. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la tomate.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint poser. Un camarade attend. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la tomate.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint apporter. La lumière est claire. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la tomate.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la cuillère. La lumière est claire. maman montre lentement. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13183,6 +13558,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint laver. Un camarade attend. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint poser. La lumière est claire. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint apporter. Un oiseau chante. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le pain. Un oiseau chante. maman montre lentement. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14507,6 +14922,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint laver. La lumière est claire. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint poser. Un oiseau chante. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint apporter. L'eau est froide. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15514,6 +15964,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-009.xlsx
+++ b/stories/arbres/TREE-SOC-009.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Une tâche sûre. Laver une tomate. Poser une cuillère. Apporter le pain. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre l'évier, la table, ou le panier.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|Sara va vers l'évier. L'eau est froide. maman est tout près. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. maman sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Sara aide en cuisine. Comment ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Oui. Sara a retenu. Sara fait une tâche sûre. Avec un adulte. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre la tomate, la cuillère, ou le pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|Sara a choisi la tomate. La cuillère tinte. maman montre lentement. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Sara rejoint laver. Maman est près. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la tomate.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Sara rejoint poser. Ça sent le basilic. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la tomate.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,7 @@
           <t>narrateur|Sara rejoint apporter. Les mains sont mouillées. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la tomate.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3778,7 @@
           <t>narrateur|Sara a choisi la cuillère. La table est lisse. maman montre lentement. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3954,6 +3974,7 @@
           <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4121,6 +4142,7 @@
           <t>narrateur|Sara rejoint laver. Ça sent le basilic. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la cuillère.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4288,6 +4310,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4455,6 +4478,7 @@
           <t>narrateur|Sara rejoint poser. Les mains sont mouillées. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la cuillère.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4622,6 +4646,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4789,6 +4814,7 @@
           <t>narrateur|Sara rejoint apporter. Un camarade attend. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis la cuillère.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4956,6 +4982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5123,6 +5150,7 @@
           <t>narrateur|Sara a choisi le pain. Le panier est osier. maman montre lentement. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5318,6 +5346,7 @@
           <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5485,6 +5514,7 @@
           <t>narrateur|Sara rejoint laver. Les mains sont mouillées. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis le pain.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5652,6 +5682,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5819,6 +5850,7 @@
           <t>narrateur|Sara rejoint poser. Un camarade attend. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis le pain.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5986,6 +6018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6153,6 +6186,7 @@
           <t>narrateur|Sara rejoint apporter. La lumière est claire. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. maman dit merci. l'évier, puis le pain.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6320,6 +6354,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
           <t>narrateur|Sara va vers la table. La tomate est lisse. maman est tout près. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Sara aide en cuisine. Comment ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6842,6 +6879,7 @@
 maman|Je suis là.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7033,6 +7071,7 @@
           <t>narrateur|On peut prendre la tomate, la cuillère, ou le pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7200,6 +7239,7 @@
           <t>narrateur|Sara a choisi la tomate. Maman est près. maman montre lentement. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7395,6 +7435,7 @@
           <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7562,6 +7603,7 @@
           <t>narrateur|Sara rejoint laver. Ça sent le basilic. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la tomate.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7729,6 +7771,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7896,6 +7939,7 @@
           <t>narrateur|Sara rejoint poser. Les mains sont mouillées. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la tomate.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8063,6 +8107,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8230,6 +8275,7 @@
           <t>narrateur|Sara rejoint apporter. Un camarade attend. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la tomate.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8397,6 +8443,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8564,6 +8611,7 @@
           <t>narrateur|Sara a choisi la cuillère. Ça sent le basilic. maman montre lentement. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8759,6 +8807,7 @@
           <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8926,6 +8975,7 @@
           <t>narrateur|Sara rejoint laver. Les mains sont mouillées. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la cuillère.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9093,6 +9143,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9260,6 +9311,7 @@
           <t>narrateur|Sara rejoint poser. Un camarade attend. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la cuillère.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9427,6 +9479,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9594,6 +9647,7 @@
           <t>narrateur|Sara rejoint apporter. La lumière est claire. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis la cuillère.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9761,6 +9815,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9928,6 +9983,7 @@
           <t>narrateur|Sara a choisi le pain. Les mains sont mouillées. maman montre lentement. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10123,6 +10179,7 @@
           <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10290,6 +10347,7 @@
           <t>narrateur|Sara rejoint laver. Un camarade attend. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis le pain.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10457,6 +10515,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10624,6 +10683,7 @@
           <t>narrateur|Sara rejoint poser. La lumière est claire. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis le pain.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10791,6 +10851,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10958,6 +11019,7 @@
           <t>narrateur|Sara rejoint apporter. Un oiseau chante. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. maman dit merci. la table, puis le pain.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11125,6 +11187,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
           <t>narrateur|Sara va vers le panier. Le pain sent bon. maman est tout près. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Sara aide en cuisine. Comment ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|C'est juste. Sara fait une tâche sûre. Avec un adulte. Sara donne la main à maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre la tomate, la cuillère, ou le pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Sara a choisi la tomate. Un camarade attend. maman montre lentement. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Sara rejoint laver. Les mains sont mouillées. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la tomate.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Sara rejoint poser. Un camarade attend. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la tomate.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Sara rejoint apporter. La lumière est claire. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la tomate.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Sara a choisi la cuillère. La lumière est claire. maman montre lentement. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Sara rejoint laver. Un camarade attend. Sara pose la cuillère. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la cuillère.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Sara rejoint poser. La lumière est claire. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la cuillère.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Sara rejoint apporter. Un oiseau chante. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis la cuillère.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Sara a choisi le pain. Un oiseau chante. maman montre lentement. Sara lave la tomate. Sara fait une tâche sûre. Avec un adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre laver, poser, ou apporter.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Sara rejoint laver. La lumière est claire. Sara apporte le pain. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis le pain.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Sara rejoint poser. Un oiseau chante. Sara reste avec l'adulte. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis le pain.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Sara rejoint apporter. L'eau est froide. Sara essuie ses mains. Sara fait une tâche sûre. Avec un adulte. maman dit merci. le panier, puis le pain.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15971,6 +16062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15985,7 +16090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16172,6 +16277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
